--- a/planilhas/Ficha-Personagem-LUDUS.xlsx
+++ b/planilhas/Ficha-Personagem-LUDUS.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A25"/>
+  <dimension ref="A2:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -603,40 +603,47 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Amarelo o aluno preenche à mão: personagem, Focuses, Signature Move, Pack, Boons, dinheiro, anotações.</t>
+          <t>Amarelo o aluno preenche à mão: personagem, Focuses, Signature Moves, Pack, Boons, dinheiro, anotações — e os RECURSOS.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>Language Points e Spotlight Tokens são do aluno. O GM anuncia o total no debrief; o aluno anota e risca conforme gasta. Gerenciar o próprio recurso em voz alta, em inglês, faz parte do exercício — não é papel de planilha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>Azul vem do Quadro da Turma e não se edita: Growth, onde ele está na trilha, a lição do ciclo, o Language Focus de hoje, se apresenta, as ações, os Language Points e o lembrete da próxima aula.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Por que só a linha dele aparece</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>O motor no rodapé importa o quadro inteiro — é ele que mostra o botão Permitir acesso, e por isso fica visível. O bloco azul lá em cima usa VLOOKUP pelo nome em B5 e mostra só a linha do próprio aluno. Ver a linha dos colegas não seria problema de segurança; é só ruído que não ajuda ninguém.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>A ficha segue o livro</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>As sete seções são as dez linhas do capítulo 3 do Player's Guide, na mesma ordem e com os mesmos nomes. Se o livro mudar, este arquivo é regerado de core/core.json — não se edita à mão.</t>
         </is>
@@ -653,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -766,7 +773,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>IFERROR(VLOOKUP($B$5,$A$58:$I$62,2,FALSE),"—")</f>
+        <f>IFERROR(VLOOKUP($B$5,$A$70:$I$74,2,FALSE),"—")</f>
         <v/>
       </c>
     </row>
@@ -777,7 +784,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>IFERROR(VLOOKUP($B$5,$A$58:$I$62,3,FALSE),"—")</f>
+        <f>IFERROR(VLOOKUP($B$5,$A$70:$I$74,3,FALSE),"—")</f>
         <v/>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -793,7 +800,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>IFERROR(VLOOKUP($B$5,$A$58:$I$62,4,FALSE),"—")</f>
+        <f>IFERROR(VLOOKUP($B$5,$A$70:$I$74,4,FALSE),"—")</f>
         <v/>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -809,7 +816,7 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>IFERROR(VLOOKUP($B$5,$A$58:$I$62,5,FALSE),"—")</f>
+        <f>IFERROR(VLOOKUP($B$5,$A$70:$I$74,5,FALSE),"—")</f>
         <v/>
       </c>
     </row>
@@ -820,7 +827,7 @@
         </is>
       </c>
       <c r="B17" s="10">
-        <f>IFERROR(VLOOKUP($B$5,$A$58:$I$62,6,FALSE),"—")</f>
+        <f>IFERROR(VLOOKUP($B$5,$A$70:$I$74,6,FALSE),"—")</f>
         <v/>
       </c>
     </row>
@@ -831,220 +838,220 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>IFERROR(VLOOKUP($B$5,$A$58:$I$62,7,FALSE),"—")</f>
+        <f>IFERROR(VLOOKUP($B$5,$A$70:$I$74,7,FALSE),"—")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>Lembrete — próxima aula</t>
+        </is>
+      </c>
+      <c r="B19" s="10">
+        <f>IFERROR(VLOOKUP($B$5,$A$70:$I$74,9,FALSE),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>3 — SEUS RECURSOS   ·   você gerencia, você desconta</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>Language Points</t>
         </is>
       </c>
-      <c r="B19" s="10">
-        <f>IFERROR(VLOOKUP($B$5,$A$58:$I$62,8,FALSE),"—")</f>
-        <v/>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Rerrolagens. Ganhas no debrief da sessão passada, gastas hoje.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="B22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>No fim de cada sessão o GM anuncia quantos você terá na próxima. Anote aqui e risque um a cada vez que gastar. Zera no fim da sessão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Spotlight Tokens</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B23" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>3 toda sessão, 1 por cena. Transferíveis. Não acumulam.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Lembrete — próxima aula</t>
-        </is>
-      </c>
-      <c r="B21" s="10">
-        <f>IFERROR(VLOOKUP($B$5,$A$58:$I$62,9,FALSE),"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>3 — SEUS FOCUSES   ·   +2, +1, +0 e −1, um em cada</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>3 no começo de toda sessão, 1 por cena. Dá para passar um a outro aluno, dizendo em inglês por quê. Volta a 3 na sessão seguinte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>4 — SEUS FOCUSES   ·   +2, +1, +0 e −1, um em cada</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>FOCUS</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>SEU VALOR</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>QUANDO ELE APARECE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Courage</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>You step toward danger instead of away from it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Empathy</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr"/>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>You deal with another person directly.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Wit</t>
+          <t>Courage</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr"/>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>You outthink the situation.</t>
+          <t>You step toward danger instead of away from it.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Instinct</t>
+          <t>Empathy</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr"/>
       <c r="C28" s="9" t="inlineStr">
         <is>
+          <t>You deal with another person directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Wit</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>You outthink the situation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Instinct</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
           <t>You have to trust your gut, right now.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>4 — SIGNATURE MOVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>5 — SIGNATURE MOVES   ·   até 3 ao longo da carreira</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Signature Move</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr"/>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Vem do seu Archetype. Sobe de tier nos Growth Levels 3, 7 e 12.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>5 — O QUE VOCÊ CARREGA</t>
+      <c r="B33" s="8" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>One, and it comes with your Archetype. It upgrades in tiers at Growth Levels 3, 7 and 12.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
+          <t>Cross-Training 1  (Growth 5)</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Tier 1 de OUTRO Archetype. Fica no Tier 1 para sempre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Cross-Training 2  (Growth 11)</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>O segundo, de um Archetype diferente do primeiro. Também fica no Tier 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>6 — O QUE VOCÊ CARREGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
           <t>Kit</t>
         </is>
       </c>
-      <c r="B34" s="10">
+      <c r="B38" s="10">
         <f>IFERROR(VLOOKUP($B$10,REFERENCE!$A$3:$B$6,2,FALSE),"—")</f>
         <v/>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Vem do Archetype e da Porta. Nunca é contado e nunca ocupa slot.</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Pack — slot 1</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>When your Pack is full and you want something new, say out loud — in English — what you are leaving behind and where you are leaving it. Then take the new thing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Pack — slot 2</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Pack — slot 3</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Pack — slot 4</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Pack — slot 5</t>
+          <t>Pack — slot 1</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>When your Pack is full and you want something new, say out loud — in English — what you are leaving behind and where you are leaving it. Then take the new thing.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Pack — slot 6</t>
+          <t>Pack — slot 2</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr"/>
@@ -1052,178 +1059,211 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Boons</t>
+          <t>Pack — slot 3</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr"/>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Só em Growth Moment. Não ocupam slot. Nunca somam no dado.</t>
-        </is>
-      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Pack — slot 4</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>6 — DINHEIRO   ·   coin → handful → bag → chest, dez de um faz um do seguinte</t>
-        </is>
-      </c>
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Pack — slot 5</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>A coin</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>A meal, a bed for the night, a good rope.</t>
-        </is>
-      </c>
+          <t>Pack — slot 6</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
+          <t>Boons</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Só em Growth Moment. Não ocupam slot. Nunca somam no dado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>7 — DINHEIRO   ·   coin → handful → bag → chest, dez de um faz um do seguinte</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>A coin</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>A meal, a bed for the night, a good rope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
           <t>A handful</t>
         </is>
       </c>
-      <c r="B45" s="8" t="n">
+      <c r="B49" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>Ten coins. A decent weapon, a week of lodging. Enough to matter for a week.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>A bag</t>
         </is>
       </c>
-      <c r="B46" s="8" t="n">
+      <c r="B50" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Ten handfuls. A horse, a forged document, a bribe that works.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>A chest</t>
         </is>
       </c>
-      <c r="B47" s="8" t="n">
+      <c r="B51" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Ten bags. A house, a ship, a name that opens doors. The ceiling.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Você começa com three handfuls. Pergunta de sessão zero: "Where did this money come from?"</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>7 — ANOTAÇÕES   ·   nomes, promessas, dívidas</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr"/>
-      <c r="B51" s="8" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr"/>
-      <c r="B52" s="8" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr"/>
-      <c r="B53" s="8" t="inlineStr"/>
-    </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr"/>
-      <c r="B54" s="8" t="inlineStr"/>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>8 — ANOTAÇÕES   ·   nomes, promessas, dívidas</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr"/>
+      <c r="B55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr"/>
+      <c r="B56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr"/>
+      <c r="B57" s="8" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr"/>
+      <c r="B58" s="8" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>COLE AQUI O LINK DO QUADRO DA TURMA →</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>cole o link do Quadro da Turma aqui</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>▼ MOTOR — a ligação com o Quadro. Não edite e não apague.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="12">
-        <f>IMPORTRANGE($B$55,"QUADRO!A1:I5")</f>
+    <row r="70">
+      <c r="A70" s="12">
+        <f>IMPORTRANGE($B$67,"QUADRO!A1:I5")</f>
         <v/>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>PRIMEIRA VEZ QUE VOCÊ ABRIR ESTA FICHA</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Desça até a célula A58. Ela vai estar com #REF! e um botão Permitir acesso. Clique no botão. Uma vez só, e nunca mais pede nada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Desça até a célula A70. Ela vai estar com #REF! e um botão Permitir acesso. Clique no botão. Uma vez só, e nunca mais pede nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Pronto — o bloco azul lá em cima se preenche sozinho.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Só a SUA linha aparece lá em cima. Este bloco de baixo é o motor da ligação: não é para ler, e não é para apagar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A30:C30"/>
+  <mergeCells count="8">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A54:C54"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -1240,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1594,6 +1634,50 @@
         </is>
       </c>
     </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>SIGNATURE MOVES</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>O seu</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>One, and it comes with your Archetype. It upgrades in tiers at Growth Levels 3, 7 and 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Cross-Training</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>At Growth Level 5, and again at Growth Level 11, you may take the Tier 1 Signature Move of a DIFFERENT Archetype and add it to your sheet permanently. It stays at Tier 1 forever — it never upgrades. Twice in a career, and never from the same Archetype twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Por quê</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Borrowed Moves give you range, not depth. The one that grows is the one you started with.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
